--- a/samples/예시데이터_구매현황(26.04~06).xlsx
+++ b/samples/예시데이터_구매현황(26.04~06).xlsx
@@ -555,7 +555,7 @@
         <v>3000</v>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="N3" t="str">
         <v>EA</v>
@@ -564,7 +564,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>300000</v>
+        <v>1170000</v>
       </c>
       <c r="Q3" t="str">
         <v>본사</v>
@@ -623,7 +623,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>300000</v>
+        <v>1170000</v>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>4000</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="N5" t="str">
         <v>EA</v>
@@ -682,7 +682,7 @@
         <v/>
       </c>
       <c r="P5">
-        <v>400000</v>
+        <v>1560000</v>
       </c>
       <c r="Q5" t="str">
         <v>본사</v>
@@ -741,7 +741,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>400000</v>
+        <v>1560000</v>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -791,7 +791,7 @@
         <v>1000</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="N7" t="str">
         <v>EA</v>
@@ -800,7 +800,7 @@
         <v/>
       </c>
       <c r="P7">
-        <v>100000</v>
+        <v>11000</v>
       </c>
       <c r="Q7" t="str">
         <v>본사</v>
@@ -850,7 +850,7 @@
         <v>1000</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="N8" t="str">
         <v>EA</v>
@@ -859,7 +859,7 @@
         <v/>
       </c>
       <c r="P8">
-        <v>100000</v>
+        <v>11000</v>
       </c>
       <c r="Q8" t="str">
         <v>본사</v>
@@ -918,7 +918,7 @@
         <v/>
       </c>
       <c r="P9">
-        <v>200000</v>
+        <v>22000</v>
       </c>
       <c r="Q9" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="P10">
-        <v>900000</v>
+        <v>2752000</v>
       </c>
       <c r="Q10" t="str">
         <v/>
